--- a/artfynd/A 17342-2025 artfynd.xlsx
+++ b/artfynd/A 17342-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129040154</v>
       </c>
       <c r="B2" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 17342-2025 artfynd.xlsx
+++ b/artfynd/A 17342-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129040154</v>
       </c>
       <c r="B2" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 17342-2025 artfynd.xlsx
+++ b/artfynd/A 17342-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -769,6 +769,234 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129483930</v>
+      </c>
+      <c r="B3" t="n">
+        <v>5197</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Fastarbytorp, Fastarbytorp, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>691561</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6610978</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Össeby-Garn</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Mattias Ödevidh</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Mattias Ödevidh</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129483754</v>
+      </c>
+      <c r="B4" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Fastarbytorp, Fastarbytorp, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>691551</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6610968</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Össeby-Garn</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mattias Ödevidh</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mattias Ödevidh</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17342-2025 artfynd.xlsx
+++ b/artfynd/A 17342-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129040154</v>
+        <v>129041064</v>
       </c>
       <c r="B2" t="n">
-        <v>57724</v>
+        <v>93235</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Fastarbytorp, Fastarbytorp, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>691429</v>
+        <v>691608</v>
       </c>
       <c r="R2" t="n">
-        <v>6610986</v>
+        <v>6610973</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,11 +752,21 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -756,26 +775,35 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Hällmarksmosaik med tall</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kristina  Lager</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristina  Lager</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Nya Tärnan gruppen</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129483930</v>
+        <v>129040154</v>
       </c>
       <c r="B3" t="n">
-        <v>5197</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,16 +811,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -800,29 +828,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Fastarbytorp, Fastarbytorp, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691561</v>
+        <v>691429</v>
       </c>
       <c r="R3" t="n">
-        <v>6610978</v>
+        <v>6610986</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -846,22 +865,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:11</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:11</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -876,22 +885,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mattias Ödevidh</t>
+          <t>Kristina  Lager</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mattias Ödevidh</t>
+          <t>Kristina  Lager</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129483754</v>
+        <v>112155282</v>
       </c>
       <c r="B4" t="n">
-        <v>8450</v>
+        <v>58636</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -899,39 +908,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>103044</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Fastarbytorp, Fastarbytorp, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691551</v>
+        <v>691337</v>
       </c>
       <c r="R4" t="n">
-        <v>6610968</v>
+        <v>6610931</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -958,22 +966,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +1004,346 @@
           <t>Mattias Ödevidh</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Nya Tärnan gruppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129483930</v>
+      </c>
+      <c r="B5" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Fastarbytorp, Fastarbytorp, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>691561</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6610978</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Össeby-Garn</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mattias Ödevidh</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mattias Ödevidh</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129040914</v>
+      </c>
+      <c r="B6" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Fastarbytorp, Fastarbytorp, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>691625</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6610971</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Össeby-Garn</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Tomas Fridström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tomas Fridström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129483754</v>
+      </c>
+      <c r="B7" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Fastarbytorp, Fastarbytorp, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>691551</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6610968</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Össeby-Garn</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mattias Ödevidh</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mattias Ödevidh</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17342-2025 artfynd.xlsx
+++ b/artfynd/A 17342-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ7"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1377,6 +1377,238 @@
       <c r="AZ7" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/129483754</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135612961</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101483</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Fastarbytorp, Fastarbytorp, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>691373</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6610973</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Össeby-Garn</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Mattias Ödevidh</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Mattias Ödevidh</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135612961</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135613262</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99551</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Fastarbytorp, Fastarbytorp, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>691460</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6610967</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Össeby-Garn</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Mattias Ödevidh</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Mattias Ödevidh</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135613262</t>
         </is>
       </c>
     </row>
@@ -1388,6 +1620,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 17342-2025 artfynd.xlsx
+++ b/artfynd/A 17342-2025 artfynd.xlsx
@@ -1385,7 +1385,7 @@
         <v>135612961</v>
       </c>
       <c r="B8" t="n">
-        <v>101483</v>
+        <v>101485</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>135613262</v>
       </c>
       <c r="B9" t="n">
-        <v>99551</v>
+        <v>99553</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 17342-2025 artfynd.xlsx
+++ b/artfynd/A 17342-2025 artfynd.xlsx
@@ -1385,7 +1385,7 @@
         <v>135612961</v>
       </c>
       <c r="B8" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>135613262</v>
       </c>
       <c r="B9" t="n">
-        <v>99553</v>
+        <v>99570</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 17342-2025 artfynd.xlsx
+++ b/artfynd/A 17342-2025 artfynd.xlsx
@@ -1385,7 +1385,7 @@
         <v>135612961</v>
       </c>
       <c r="B8" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>135613262</v>
       </c>
       <c r="B9" t="n">
-        <v>99570</v>
+        <v>99571</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 17342-2025 artfynd.xlsx
+++ b/artfynd/A 17342-2025 artfynd.xlsx
@@ -1385,7 +1385,7 @@
         <v>135612961</v>
       </c>
       <c r="B8" t="n">
-        <v>101504</v>
+        <v>101505</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>135613262</v>
       </c>
       <c r="B9" t="n">
-        <v>99571</v>
+        <v>99572</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 17342-2025 artfynd.xlsx
+++ b/artfynd/A 17342-2025 artfynd.xlsx
@@ -1385,7 +1385,7 @@
         <v>135612961</v>
       </c>
       <c r="B8" t="n">
-        <v>101505</v>
+        <v>101506</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>135613262</v>
       </c>
       <c r="B9" t="n">
-        <v>99572</v>
+        <v>99573</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 17342-2025 artfynd.xlsx
+++ b/artfynd/A 17342-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ9"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,42 +680,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129041064</v>
+        <v>136375999</v>
       </c>
       <c r="B2" t="n">
-        <v>93235</v>
+        <v>96539</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>2812</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>691608</v>
+        <v>691423</v>
       </c>
       <c r="R2" t="n">
-        <v>6610973</v>
+        <v>6610990</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,22 +749,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,40 +775,31 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Hällmarksmosaik med tall</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Mattias Ödevidh</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Nya Tärnan gruppen</t>
-        </is>
-      </c>
+          <t>Mattias Ödevidh</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129041064</t>
+          <t>https://artportalen.se/Sighting/136375999</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129040154</v>
+        <v>136376668</v>
       </c>
       <c r="B3" t="n">
-        <v>57950</v>
+        <v>92301</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -821,37 +807,41 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>3008</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Timmerticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Amyloporia sinuosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Fr.) Rajchenb. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Fastarbytorp, Fastarbytorp, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691429</v>
+        <v>691493</v>
       </c>
       <c r="R3" t="n">
-        <v>6610986</v>
+        <v>6611034</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,12 +865,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,73 +891,93 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristina  Lager</t>
+          <t>Mattias Ödevidh</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristina  Lager</t>
+          <t>Mattias Ödevidh</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129040154</t>
+          <t>https://artportalen.se/Sighting/136376668</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112155282</v>
+        <v>129041064</v>
       </c>
       <c r="B4" t="n">
-        <v>58636</v>
+        <v>93235</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103044</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Fastarbytorp, Fastarbytorp, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691337</v>
+        <v>691608</v>
       </c>
       <c r="R4" t="n">
-        <v>6610931</v>
+        <v>6610973</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,22 +1001,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,16 +1027,21 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Hällmarksmosaik med tall</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Mattias Ödevidh</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mattias Ödevidh</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1026,16 +1051,16 @@
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112155282</t>
+          <t>https://artportalen.se/Sighting/129041064</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129483930</v>
+        <v>129040154</v>
       </c>
       <c r="B5" t="n">
-        <v>5199</v>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1043,16 +1068,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1060,29 +1085,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Fastarbytorp, Fastarbytorp, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691561</v>
+        <v>691429</v>
       </c>
       <c r="R5" t="n">
-        <v>6610978</v>
+        <v>6610986</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1106,22 +1122,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>11:11</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>11:11</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,27 +1142,27 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Mattias Ödevidh</t>
+          <t>Kristina  Lager</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Mattias Ödevidh</t>
+          <t>Kristina  Lager</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129483930</t>
+          <t>https://artportalen.se/Sighting/129040154</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129040914</v>
+        <v>112155282</v>
       </c>
       <c r="B6" t="n">
-        <v>8455</v>
+        <v>58636</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1164,37 +1170,41 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>103044</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Fastarbytorp, Fastarbytorp, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691625</v>
+        <v>691337</v>
       </c>
       <c r="R6" t="n">
-        <v>6610971</v>
+        <v>6610931</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1218,22 +1228,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,27 +1258,31 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Tomas Fridström</t>
+          <t>Mattias Ödevidh</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Tomas Fridström</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Mattias Ödevidh</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Nya Tärnan gruppen</t>
+        </is>
+      </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129040914</t>
+          <t>https://artportalen.se/Sighting/112155282</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129483754</v>
+        <v>129483930</v>
       </c>
       <c r="B7" t="n">
-        <v>8455</v>
+        <v>5199</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,24 +1290,28 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>105930</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
@@ -1305,10 +1323,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>691551</v>
+        <v>691561</v>
       </c>
       <c r="R7" t="n">
-        <v>6610968</v>
+        <v>6610978</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1340,7 +1358,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1350,7 +1368,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,16 +1394,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129483754</t>
+          <t>https://artportalen.se/Sighting/129483930</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135612961</v>
+        <v>129040914</v>
       </c>
       <c r="B8" t="n">
-        <v>101506</v>
+        <v>8455</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,41 +1411,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Fastarbytorp, Fastarbytorp, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>691373</v>
+        <v>691625</v>
       </c>
       <c r="R8" t="n">
-        <v>6610973</v>
+        <v>6610971</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1451,22 +1465,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1481,27 +1495,27 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Mattias Ödevidh</t>
+          <t>Tomas Fridström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Mattias Ödevidh</t>
+          <t>Tomas Fridström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135612961</t>
+          <t>https://artportalen.se/Sighting/129040914</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135613262</v>
+        <v>129483754</v>
       </c>
       <c r="B9" t="n">
-        <v>99573</v>
+        <v>8455</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1509,26 +1523,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222812</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Convallaria majalis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>100</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1537,10 +1552,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>691460</v>
+        <v>691551</v>
       </c>
       <c r="R9" t="n">
-        <v>6610967</v>
+        <v>6610968</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1567,22 +1582,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2025-11-02</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2025-11-02</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1607,6 +1622,596 @@
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129483754</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136376468</v>
+      </c>
+      <c r="B10" t="n">
+        <v>8463</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Fastarbytorp, Fastarbytorp, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>691463</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6611001</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Össeby-Garn</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Mattias Ödevidh</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Mattias Ödevidh</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136376468</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136376349</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98189</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Fastarbytorp, Fastarbytorp, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>691463</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6611001</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Össeby-Garn</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Mattias Ödevidh</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Mattias Ödevidh</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136376349</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135612961</v>
+      </c>
+      <c r="B12" t="n">
+        <v>101506</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Fastarbytorp, Fastarbytorp, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>691373</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6610973</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Össeby-Garn</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Mattias Ödevidh</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Mattias Ödevidh</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135612961</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136375904</v>
+      </c>
+      <c r="B13" t="n">
+        <v>101537</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Fastarbytorp, Fastarbytorp, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>691403</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6610991</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Össeby-Garn</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Mattias Ödevidh</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Mattias Ödevidh</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136375904</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135613262</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99573</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Fastarbytorp, Fastarbytorp, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>691460</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6610967</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Össeby-Garn</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Mattias Ödevidh</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Mattias Ödevidh</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135613262</t>
         </is>
@@ -1622,6 +2227,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 17342-2025 artfynd.xlsx
+++ b/artfynd/A 17342-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136375999</v>
       </c>
       <c r="B2" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136376668</v>
       </c>
       <c r="B3" t="n">
-        <v>92301</v>
+        <v>92302</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>136376349</v>
       </c>
       <c r="B11" t="n">
-        <v>98189</v>
+        <v>98190</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>136375904</v>
       </c>
       <c r="B13" t="n">
-        <v>101537</v>
+        <v>101538</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 17342-2025 artfynd.xlsx
+++ b/artfynd/A 17342-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136375999</v>
       </c>
       <c r="B2" t="n">
-        <v>96540</v>
+        <v>96553</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136376668</v>
       </c>
       <c r="B3" t="n">
-        <v>92302</v>
+        <v>92315</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>136376349</v>
       </c>
       <c r="B11" t="n">
-        <v>98190</v>
+        <v>98203</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>136375904</v>
       </c>
       <c r="B13" t="n">
-        <v>101538</v>
+        <v>101551</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 17342-2025 artfynd.xlsx
+++ b/artfynd/A 17342-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136375999</v>
       </c>
       <c r="B2" t="n">
-        <v>96553</v>
+        <v>96554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136376668</v>
       </c>
       <c r="B3" t="n">
-        <v>92315</v>
+        <v>92316</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>136376349</v>
       </c>
       <c r="B11" t="n">
-        <v>98203</v>
+        <v>98204</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>136375904</v>
       </c>
       <c r="B13" t="n">
-        <v>101551</v>
+        <v>101552</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
